--- a/output/pdf_financials_xlsx/PTC.xlsx
+++ b/output/pdf_financials_xlsx/PTC.xlsx
@@ -1025,19 +1025,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.005233</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.007757</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000214</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000166</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1956,16 +1956,16 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.555702</v>
+        <v>-0.563459</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.14791</v>
+        <v>-1.148124</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-0.577686</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.445483</v>
+        <v>-2.445649</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.148023</v>
@@ -2078,16 +2078,16 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.365421</v>
+        <v>-0.373178</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.857752</v>
+        <v>-0.857966</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.290975</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.228399</v>
+        <v>-2.228565</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.02222</v>
@@ -2140,16 +2140,16 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-63.58354648431382</v>
+        <v>-64.93327069304519</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-158.1010591041299</v>
+        <v>-158.1405036366384</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>-58.90301423105731</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-378.8441202971728</v>
+        <v>-378.8723415106849</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>-3.423006237512266</v>
@@ -2328,31 +2328,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>3.231692</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.669244</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.426463</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.335342</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.260195</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.295605</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.27491</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.07012599999999999</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.13401</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0.205947</v>
@@ -2420,31 +2420,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>3.231692</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.669244</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.426463</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.335342</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.260195</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.295605</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.27491</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.07012599999999999</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.13401</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0.205947</v>
@@ -2972,31 +2972,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>3.301077</v>
+        <v>0.069385</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.679334</v>
+        <v>0.01009</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.446346</v>
+        <v>0.019883</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.349063</v>
+        <v>0.013721</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.266902</v>
+        <v>0.006707</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.302565</v>
+        <v>0.00696</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.276598</v>
+        <v>0.001688</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.07076399999999999</v>
+        <v>0.000638</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.134648</v>
+        <v>0.000638</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0</v>
@@ -10106,7 +10106,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
@@ -19509,11 +19509,7 @@
           <t>General and administrative fees</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" s="5" t="n">
         <v>0.608818</v>
       </c>
@@ -19971,7 +19967,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E166" s="5" t="n">
@@ -20905,7 +20901,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">

--- a/output/pdf_financials_xlsx/PTC.xlsx
+++ b/output/pdf_financials_xlsx/PTC.xlsx
@@ -1735,10 +1735,8 @@
       <c r="H23" s="3" t="n">
         <v>-0.103774</v>
       </c>
-      <c r="I23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I23" s="3" t="n">
+        <v>-0.418954</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>0.111492</v>
@@ -5405,10 +5403,8 @@
       <c r="H99" s="3" t="n">
         <v>-0.103774</v>
       </c>
-      <c r="I99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I99" s="3" t="n">
+        <v>-0.418954</v>
       </c>
       <c r="J99" s="3" t="n">
         <v>0.111492</v>
@@ -5896,40 +5892,40 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.008326999999999999</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.002153</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.004373</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.006161</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.007417</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.005937</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.006141</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.009438999999999999</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.010606</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.008536999999999999</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.008330000000000001</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.009534000000000001</v>
       </c>
     </row>
     <row r="111">
@@ -13262,7 +13258,11 @@
           <t>Accretion expense 6</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -13495,7 +13495,11 @@
           <t>Deferred tax recovery 8</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -15047,7 +15051,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -17040,7 +17048,11 @@
           <t>Accretion 7</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -17682,7 +17694,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -18233,7 +18249,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
